--- a/outputs/results/all_results_cnn.xlsx
+++ b/outputs/results/all_results_cnn.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard_ภาพรวม" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Detailed_Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_ภาพรวม" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed_Results" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detailed_Results'!$A$1:$F$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detailed_Results'!$A$1:$F$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -618,10 +618,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="128" customWidth="1" min="1" max="1"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>สร้างรายงานเมื่อ: 2026-10-21 00:32:55 | โมเดลที่ใช้ตรวจ: Custom 2D CNN (CharCNN 93.78%) | ตรวจทั้งหมด: 9 แผ่น | รวม 180 ข้อ</t>
+          <t>สร้างรายงานเมื่อ: 2026-10-26 14:43:36 | โมเดลที่ใช้ตรวจ: Custom 2D CNN | ตรวจทั้งหมด: 12 แผ่น | รวม 240 ข้อ</t>
         </is>
       </c>
     </row>
@@ -676,27 +676,27 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>9 แผ่น</t>
+          <t>12 แผ่น</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>180 ข้อ</t>
+          <t>240 ข้อ</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>3,600 ตัว</t>
+          <t>4,800 ตัว</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>93.67%</t>
+          <t>95.04%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>131 ข้อ</t>
+          <t>185 ข้อ</t>
         </is>
       </c>
     </row>
@@ -760,17 +760,17 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>97.50%</t>
+          <t>98.75%</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>0.964</t>
+          <t>0.956</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>10 ข้อ</t>
+          <t>12 ข้อ</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>82.00%</t>
+          <t>84.00%</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>0.870</t>
+          <t>0.858</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>0.941</t>
+          <t>0.938</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>16 ข้อ</t>
+          <t>17 ข้อ</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>97.50%</t>
+          <t>99.50%</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>0.964</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>13 ข้อ</t>
+          <t>11 ข้อ</t>
         </is>
       </c>
       <c r="G14" s="11" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>94.00%</t>
+          <t>93.25%</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>0.939</t>
+          <t>0.927</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>17 ข้อ</t>
+          <t>19 ข้อ</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -925,17 +925,17 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>95.50%</t>
+          <t>97.25%</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>0.957</t>
+          <t>0.955</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>10 ข้อ</t>
+          <t>12 ข้อ</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>95.00%</t>
+          <t>97.25%</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>0.961</t>
+          <t>0.956</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>13 ข้อ</t>
+          <t>15 ข้อ</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>93.25%</t>
+          <t>94.25%</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>0.916</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -1024,20 +1024,119 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>92.50%</t>
+          <t>93.50%</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>0.920</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>14 ข้อ</t>
+          <t>20 ข้อ</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>English &amp; Tech (ชุดที่ 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>89.50%</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>0.889</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>19 ข้อ</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>English &amp; Tech (ชุดที่ 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>98.25%</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>0.952</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>12 ข้อ</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>English &amp; Tech (ชุดที่ 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>99.25%</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>0.953</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>10 ข้อ</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>English &amp; Tech (ชุดที่ 1)</t>
         </is>
@@ -1057,10 +1156,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F181"/>
+  <dimension ref="A1:F241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -1111,14 +1210,14 @@
       </c>
       <c r="C2" s="14" t="inlineStr">
         <is>
-          <t>THE-QUICK-BROWN-EOX-</t>
+          <t>THE-QUICK-BROWN-FOX-</t>
         </is>
       </c>
       <c r="D2" s="15" t="n">
-        <v>0.952</v>
+        <v>0.955</v>
       </c>
       <c r="E2" s="15" t="n">
-        <v>0.639</v>
+        <v>0.701</v>
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
@@ -1137,18 +1236,18 @@
       </c>
       <c r="C3" s="18" t="inlineStr">
         <is>
-          <t>JUMPS-OVER-LAZY-DOG-</t>
+          <t>JUMPS-OVER-LAZY-COG-</t>
         </is>
       </c>
       <c r="D3" s="19" t="n">
-        <v>0.977</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="E3" s="19" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.293</v>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -1167,10 +1266,10 @@
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>0.96</v>
+        <v>0.955</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.62</v>
+        <v>0.679</v>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
@@ -1189,14 +1288,14 @@
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>EIVE-DOZEN-LIQUOR-JU</t>
+          <t>FIVE-DOZEN-LIQUOR-JU</t>
         </is>
       </c>
       <c r="D5" s="19" t="n">
-        <v>0.952</v>
+        <v>0.965</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.905</v>
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
@@ -1215,14 +1314,14 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>SPHINX-OE-BLACK-GEM-</t>
+          <t>SPHINX-OF-BLACK-GEM-</t>
         </is>
       </c>
       <c r="D6" s="15" t="n">
-        <v>0.979</v>
+        <v>0.968</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>0.85</v>
+        <v>0.834</v>
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
@@ -1245,10 +1344,10 @@
         </is>
       </c>
       <c r="D7" s="19" t="n">
-        <v>0.967</v>
+        <v>0.96</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.843</v>
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
@@ -1271,10 +1370,10 @@
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>0.987</v>
+        <v>0.985</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.947</v>
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
@@ -1297,10 +1396,10 @@
         </is>
       </c>
       <c r="D9" s="19" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.952</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>0.495</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
@@ -1323,14 +1422,14 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>0.986</v>
+        <v>0.955</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.749</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -1349,10 +1448,10 @@
         </is>
       </c>
       <c r="D11" s="19" t="n">
-        <v>0.945</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>0.608</v>
+        <v>0.592</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
@@ -1375,10 +1474,10 @@
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>0.955</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>0.503</v>
+        <v>0.476</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
@@ -1404,7 +1503,7 @@
         <v>0.984</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>0.907</v>
+        <v>0.923</v>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
@@ -1427,10 +1526,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>0.978</v>
+        <v>0.972</v>
       </c>
       <c r="E14" s="15" t="n">
-        <v>0.855</v>
+        <v>0.82</v>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
@@ -1453,10 +1552,10 @@
         </is>
       </c>
       <c r="D15" s="19" t="n">
-        <v>0.952</v>
+        <v>0.951</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>0.708</v>
+        <v>0.73</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
@@ -1475,14 +1574,14 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>ARTIEICIAL-SYSTGM-OK</t>
+          <t>ARTIEICIAL-SYSTEM-OK</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>0.946</v>
+        <v>0.92</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>0.522</v>
+        <v>0.354</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -1505,14 +1604,14 @@
         </is>
       </c>
       <c r="D17" s="19" t="n">
-        <v>0.963</v>
+        <v>0.965</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>0.697</v>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0.825</v>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -1531,10 +1630,10 @@
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>0.966</v>
+        <v>0.961</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>0.587</v>
+        <v>0.53</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -1553,18 +1652,18 @@
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>EIND-EXTRA-EIND-GOLD</t>
+          <t>FIND-EXTRA-FIND-GOLD</t>
         </is>
       </c>
       <c r="D19" s="19" t="n">
-        <v>0.955</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="E19" s="19" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.668</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -1583,10 +1682,10 @@
         </is>
       </c>
       <c r="D20" s="15" t="n">
-        <v>0.96</v>
+        <v>0.955</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>0.661</v>
+        <v>0.714</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
@@ -1609,10 +1708,10 @@
         </is>
       </c>
       <c r="D21" s="19" t="n">
-        <v>0.971</v>
+        <v>0.97</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
@@ -1631,14 +1730,14 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>TIL-QULCK-BROWN-FQX-</t>
+          <t>TIL-QULCK-BROWN-FCX-</t>
         </is>
       </c>
       <c r="D22" s="15" t="n">
-        <v>0.879</v>
+        <v>0.875</v>
       </c>
       <c r="E22" s="15" t="n">
-        <v>0.491</v>
+        <v>0.366</v>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
@@ -1657,14 +1756,14 @@
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>JUMPS-OVER-LAZY-CQG-</t>
+          <t>JUMMS-OVER-LAZY-CQG-</t>
         </is>
       </c>
       <c r="D23" s="19" t="n">
-        <v>0.886</v>
+        <v>0.883</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>0.397</v>
+        <v>0.444</v>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
@@ -1687,10 +1786,10 @@
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>0.953</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>0.636</v>
+        <v>0.593</v>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
@@ -1709,14 +1808,14 @@
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>EIVE-DOZEN-LIQUOR-JV</t>
+          <t>FIVE-DOZEN-LIQUOR-JU</t>
         </is>
       </c>
       <c r="D25" s="19" t="n">
-        <v>0.865</v>
+        <v>0.856</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>0.425</v>
+        <v>0.519</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
@@ -1735,14 +1834,14 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>SPHUNX-OE-BUACK-GEM-</t>
+          <t>SPHUNX-OF-BUACK-GFM-</t>
         </is>
       </c>
       <c r="D26" s="15" t="n">
-        <v>0.893</v>
+        <v>0.88</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>0.482</v>
+        <v>0.333</v>
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
@@ -1765,10 +1864,10 @@
         </is>
       </c>
       <c r="D27" s="19" t="n">
-        <v>0.91</v>
+        <v>0.898</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>0.333</v>
+        <v>0.477</v>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
@@ -1787,14 +1886,14 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>RR-GHI-LEPHYRS-KLQW-</t>
+          <t>BR-GHI-LEPHYRS-BLOW-</t>
         </is>
       </c>
       <c r="D28" s="15" t="n">
-        <v>0.889</v>
+        <v>0.848</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>0.196</v>
+        <v>0.214</v>
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
@@ -1817,10 +1916,10 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>0.912</v>
+        <v>0.898</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>0.319</v>
+        <v>0.141</v>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
@@ -1839,14 +1938,14 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>MACHINEILEARNING-AJ-</t>
+          <t>MACHINE-LEARNING-AJ-</t>
         </is>
       </c>
       <c r="D30" s="15" t="n">
-        <v>0.892</v>
+        <v>0.924</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.119</v>
+        <v>0.712</v>
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
@@ -1865,14 +1964,14 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>DEEP-NEURAU-NFTMQRKS</t>
+          <t>DEEP-NEURAU-NFTMORKS</t>
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>0.829</v>
+        <v>0.776</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>0.437</v>
+        <v>0.353</v>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
@@ -1891,14 +1990,14 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>-MAGE-DATA-DEUFCT-CK</t>
+          <t>-MAGE-DATA-DELFCT-CK</t>
         </is>
       </c>
       <c r="D32" s="15" t="n">
-        <v>0.826</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>0.335</v>
+        <v>0.4</v>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
@@ -1917,14 +2016,14 @@
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>DYIHON-OPENCV-BOBCT-</t>
+          <t>DYIHON-OPFNCV-BOBCT-</t>
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>0.903</v>
+        <v>0.891</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>0.554</v>
+        <v>0.571</v>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
@@ -1943,14 +2042,14 @@
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>SMATT-CCR-RECCGWIZE-</t>
+          <t>SMART-CCR-BECCGWIZD-</t>
         </is>
       </c>
       <c r="D34" s="15" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.847</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>0.248</v>
+        <v>0.319</v>
       </c>
       <c r="F34" s="16" t="inlineStr">
         <is>
@@ -1969,14 +2068,14 @@
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>ACCUKATF--REDICTJBN-</t>
+          <t>ACCUKATF--BEDICTJBN-</t>
         </is>
       </c>
       <c r="D35" s="19" t="n">
-        <v>0.852</v>
+        <v>0.802</v>
       </c>
       <c r="E35" s="19" t="n">
-        <v>0.45</v>
+        <v>0.309</v>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
@@ -1995,14 +2094,14 @@
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>ARTIFICJAI-SYSTEM-CK</t>
+          <t>ARTIFICJAL-SYSTEM-CK</t>
         </is>
       </c>
       <c r="D36" s="15" t="n">
-        <v>0.87</v>
+        <v>0.859</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>0.424</v>
+        <v>0.499</v>
       </c>
       <c r="F36" s="16" t="inlineStr">
         <is>
@@ -2025,10 +2124,10 @@
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>0.891</v>
+        <v>0.843</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>0.576</v>
+        <v>0.273</v>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
@@ -2047,14 +2146,14 @@
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>KNOWLICCFDIS-PQWEB--</t>
+          <t>KNOWL-CCFCIS-PQWEB--</t>
         </is>
       </c>
       <c r="D38" s="15" t="n">
-        <v>0.834</v>
+        <v>0.864</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>0.173</v>
+        <v>0.33</v>
       </c>
       <c r="F38" s="16" t="inlineStr">
         <is>
@@ -2073,14 +2172,14 @@
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>EIND-FXTRA-HINE-GDLD</t>
+          <t>FIND-FXTRA-FINF-GPLD</t>
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>0.854</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>0.373</v>
+        <v>0.2</v>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
@@ -2099,14 +2198,14 @@
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>ZERQ-ONF--WG-SIX-TEC</t>
+          <t>ZERO-ONF--WG-SIX-TEN</t>
         </is>
       </c>
       <c r="D40" s="15" t="n">
-        <v>0.793</v>
+        <v>0.825</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>0.277</v>
+        <v>0.314</v>
       </c>
       <c r="F40" s="16" t="inlineStr">
         <is>
@@ -2125,14 +2224,14 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>ABCDEFGHIJKL-NCHGRQT</t>
+          <t>ABCDEFGHIJKL-NCAGRST</t>
         </is>
       </c>
       <c r="D41" s="19" t="n">
-        <v>0.848</v>
+        <v>0.843</v>
       </c>
       <c r="E41" s="19" t="n">
-        <v>0.307</v>
+        <v>0.27</v>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
@@ -2155,14 +2254,14 @@
         </is>
       </c>
       <c r="D42" s="15" t="n">
-        <v>0.974</v>
+        <v>0.959</v>
       </c>
       <c r="E42" s="15" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="F42" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.784</v>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -2181,10 +2280,10 @@
         </is>
       </c>
       <c r="D43" s="19" t="n">
-        <v>0.961</v>
+        <v>0.958</v>
       </c>
       <c r="E43" s="19" t="n">
-        <v>0.779</v>
+        <v>0.725</v>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
@@ -2207,10 +2306,10 @@
         </is>
       </c>
       <c r="D44" s="15" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.925</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>0.327</v>
+        <v>0.29</v>
       </c>
       <c r="F44" s="16" t="inlineStr">
         <is>
@@ -2233,14 +2332,14 @@
         </is>
       </c>
       <c r="D45" s="19" t="n">
-        <v>0.964</v>
+        <v>0.951</v>
       </c>
       <c r="E45" s="19" t="n">
-        <v>0.734</v>
-      </c>
-      <c r="F45" s="16" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -2259,10 +2358,10 @@
         </is>
       </c>
       <c r="D46" s="15" t="n">
-        <v>0.959</v>
+        <v>0.929</v>
       </c>
       <c r="E46" s="15" t="n">
-        <v>0.798</v>
+        <v>0.737</v>
       </c>
       <c r="F46" s="16" t="inlineStr">
         <is>
@@ -2285,14 +2384,14 @@
         </is>
       </c>
       <c r="D47" s="19" t="n">
-        <v>0.967</v>
+        <v>0.953</v>
       </c>
       <c r="E47" s="19" t="n">
-        <v>0.804</v>
-      </c>
-      <c r="F47" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.721</v>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -2311,10 +2410,10 @@
         </is>
       </c>
       <c r="D48" s="15" t="n">
-        <v>0.952</v>
+        <v>0.955</v>
       </c>
       <c r="E48" s="15" t="n">
-        <v>0.532</v>
+        <v>0.777</v>
       </c>
       <c r="F48" s="16" t="inlineStr">
         <is>
@@ -2337,10 +2436,10 @@
         </is>
       </c>
       <c r="D49" s="19" t="n">
-        <v>0.947</v>
+        <v>0.945</v>
       </c>
       <c r="E49" s="19" t="n">
-        <v>0.729</v>
+        <v>0.613</v>
       </c>
       <c r="F49" s="16" t="inlineStr">
         <is>
@@ -2363,10 +2462,10 @@
         </is>
       </c>
       <c r="D50" s="15" t="n">
-        <v>0.958</v>
+        <v>0.964</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.711</v>
       </c>
       <c r="F50" s="16" t="inlineStr">
         <is>
@@ -2389,10 +2488,10 @@
         </is>
       </c>
       <c r="D51" s="19" t="n">
-        <v>0.952</v>
+        <v>0.951</v>
       </c>
       <c r="E51" s="19" t="n">
-        <v>0.506</v>
+        <v>0.703</v>
       </c>
       <c r="F51" s="16" t="inlineStr">
         <is>
@@ -2415,14 +2514,14 @@
         </is>
       </c>
       <c r="D52" s="15" t="n">
-        <v>0.984</v>
+        <v>0.957</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="F52" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.647</v>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -2437,14 +2536,14 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>SYTHONPDPENUVDROBDT-</t>
+          <t>FYTHONCDPENUVRROBDT-</t>
         </is>
       </c>
       <c r="D53" s="19" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.829</v>
       </c>
       <c r="E53" s="19" t="n">
-        <v>0.175</v>
+        <v>0.187</v>
       </c>
       <c r="F53" s="16" t="inlineStr">
         <is>
@@ -2467,10 +2566,10 @@
         </is>
       </c>
       <c r="D54" s="15" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.929</v>
       </c>
       <c r="E54" s="15" t="n">
-        <v>0.583</v>
+        <v>0.616</v>
       </c>
       <c r="F54" s="16" t="inlineStr">
         <is>
@@ -2489,14 +2588,14 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>ACCURATE-PREDICTION-</t>
+          <t>ACCURATE-DREDICTION-</t>
         </is>
       </c>
       <c r="D55" s="19" t="n">
-        <v>0.916</v>
+        <v>0.902</v>
       </c>
       <c r="E55" s="19" t="n">
-        <v>0.475</v>
+        <v>0.453</v>
       </c>
       <c r="F55" s="16" t="inlineStr">
         <is>
@@ -2519,10 +2618,10 @@
         </is>
       </c>
       <c r="D56" s="15" t="n">
-        <v>0.921</v>
+        <v>0.931</v>
       </c>
       <c r="E56" s="15" t="n">
-        <v>0.485</v>
+        <v>0.645</v>
       </c>
       <c r="F56" s="16" t="inlineStr">
         <is>
@@ -2545,10 +2644,10 @@
         </is>
       </c>
       <c r="D57" s="19" t="n">
-        <v>0.913</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E57" s="19" t="n">
-        <v>0.366</v>
+        <v>0.576</v>
       </c>
       <c r="F57" s="16" t="inlineStr">
         <is>
@@ -2571,10 +2670,10 @@
         </is>
       </c>
       <c r="D58" s="15" t="n">
-        <v>0.927</v>
+        <v>0.923</v>
       </c>
       <c r="E58" s="15" t="n">
-        <v>0.453</v>
+        <v>0.393</v>
       </c>
       <c r="F58" s="16" t="inlineStr">
         <is>
@@ -2593,18 +2692,18 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>EIND-EXTRA-EIND-GOLD</t>
+          <t>FIND-EXTRA-FIND-GOLD</t>
         </is>
       </c>
       <c r="D59" s="19" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="E59" s="19" t="n">
-        <v>0.498</v>
-      </c>
-      <c r="F59" s="16" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0.839</v>
+      </c>
+      <c r="F59" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -2619,14 +2718,14 @@
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>ZERO-ONE-TWO-SIX-TEN</t>
+          <t>ZERO-ONK-TWO-SIX-TEN</t>
         </is>
       </c>
       <c r="D60" s="15" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>0.424</v>
+        <v>0.39</v>
       </c>
       <c r="F60" s="16" t="inlineStr">
         <is>
@@ -2652,7 +2751,7 @@
         <v>0.968</v>
       </c>
       <c r="E61" s="19" t="n">
-        <v>0.842</v>
+        <v>0.867</v>
       </c>
       <c r="F61" s="20" t="inlineStr">
         <is>
@@ -2671,18 +2770,18 @@
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>THE-QUICK-BRONN-EOX-</t>
+          <t>THE-QUICK-BROWN-FOX-</t>
         </is>
       </c>
       <c r="D62" s="15" t="n">
-        <v>0.952</v>
+        <v>0.957</v>
       </c>
       <c r="E62" s="15" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="F62" s="16" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0.801</v>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -2701,10 +2800,10 @@
         </is>
       </c>
       <c r="D63" s="19" t="n">
-        <v>0.968</v>
+        <v>0.963</v>
       </c>
       <c r="E63" s="19" t="n">
-        <v>0.771</v>
+        <v>0.678</v>
       </c>
       <c r="F63" s="16" t="inlineStr">
         <is>
@@ -2727,14 +2826,14 @@
         </is>
       </c>
       <c r="D64" s="15" t="n">
-        <v>0.967</v>
+        <v>0.969</v>
       </c>
       <c r="E64" s="15" t="n">
-        <v>0.717</v>
-      </c>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0.848</v>
+      </c>
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -2749,14 +2848,14 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>EIVE-DOZEN-LIQUOR-JU</t>
+          <t>FIVE-DOZEN-LIQUOR-JU</t>
         </is>
       </c>
       <c r="D65" s="19" t="n">
-        <v>0.977</v>
+        <v>0.97</v>
       </c>
       <c r="E65" s="19" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
@@ -2775,14 +2874,14 @@
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>SPHINX-OE-BLACK-GEM-</t>
+          <t>SPHINX-OF-BLACK-GEM-</t>
         </is>
       </c>
       <c r="D66" s="15" t="n">
-        <v>0.981</v>
+        <v>0.978</v>
       </c>
       <c r="E66" s="15" t="n">
-        <v>0.85</v>
+        <v>0.834</v>
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
@@ -2805,10 +2904,10 @@
         </is>
       </c>
       <c r="D67" s="19" t="n">
-        <v>0.947</v>
+        <v>0.956</v>
       </c>
       <c r="E67" s="19" t="n">
-        <v>0.656</v>
+        <v>0.706</v>
       </c>
       <c r="F67" s="16" t="inlineStr">
         <is>
@@ -2831,10 +2930,10 @@
         </is>
       </c>
       <c r="D68" s="15" t="n">
-        <v>0.982</v>
+        <v>0.98</v>
       </c>
       <c r="E68" s="15" t="n">
-        <v>0.928</v>
+        <v>0.883</v>
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
@@ -2860,7 +2959,7 @@
         <v>0.966</v>
       </c>
       <c r="E69" s="19" t="n">
-        <v>0.776</v>
+        <v>0.784</v>
       </c>
       <c r="F69" s="16" t="inlineStr">
         <is>
@@ -2883,14 +2982,14 @@
         </is>
       </c>
       <c r="D70" s="15" t="n">
-        <v>0.977</v>
+        <v>0.975</v>
       </c>
       <c r="E70" s="15" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="F70" s="16" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0.835</v>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -2909,10 +3008,10 @@
         </is>
       </c>
       <c r="D71" s="19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.949</v>
       </c>
       <c r="E71" s="19" t="n">
-        <v>0.677</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F71" s="16" t="inlineStr">
         <is>
@@ -2931,14 +3030,14 @@
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>IMAGE-DATA-DETEOT-OK</t>
+          <t>IMAGE-DATA-DETECT-OK</t>
         </is>
       </c>
       <c r="D72" s="15" t="n">
-        <v>0.963</v>
+        <v>0.964</v>
       </c>
       <c r="E72" s="15" t="n">
-        <v>0.837</v>
+        <v>0.835</v>
       </c>
       <c r="F72" s="20" t="inlineStr">
         <is>
@@ -2961,10 +3060,10 @@
         </is>
       </c>
       <c r="D73" s="19" t="n">
-        <v>0.965</v>
+        <v>0.967</v>
       </c>
       <c r="E73" s="19" t="n">
-        <v>0.763</v>
+        <v>0.762</v>
       </c>
       <c r="F73" s="16" t="inlineStr">
         <is>
@@ -2987,10 +3086,10 @@
         </is>
       </c>
       <c r="D74" s="15" t="n">
-        <v>0.982</v>
+        <v>0.971</v>
       </c>
       <c r="E74" s="15" t="n">
-        <v>0.945</v>
+        <v>0.883</v>
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
@@ -3013,7 +3112,7 @@
         </is>
       </c>
       <c r="D75" s="19" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.951</v>
       </c>
       <c r="E75" s="19" t="n">
         <v>0.705</v>
@@ -3035,18 +3134,18 @@
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>ARTIEICIAL-SYSTEM-OK</t>
+          <t>ARTIFICIAL-SYSTEM-OK</t>
         </is>
       </c>
       <c r="D76" s="15" t="n">
-        <v>0.97</v>
+        <v>0.969</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F76" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.787</v>
+      </c>
+      <c r="F76" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3167,7 @@
         <v>0.966</v>
       </c>
       <c r="E77" s="19" t="n">
-        <v>0.724</v>
+        <v>0.681</v>
       </c>
       <c r="F77" s="16" t="inlineStr">
         <is>
@@ -3091,10 +3190,10 @@
         </is>
       </c>
       <c r="D78" s="15" t="n">
-        <v>0.964</v>
+        <v>0.973</v>
       </c>
       <c r="E78" s="15" t="n">
-        <v>0.643</v>
+        <v>0.727</v>
       </c>
       <c r="F78" s="16" t="inlineStr">
         <is>
@@ -3113,14 +3212,14 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>EIND-EXTRA-FINO-GOLD</t>
+          <t>FIND-EXTRA-FIND-GOLD</t>
         </is>
       </c>
       <c r="D79" s="19" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E79" s="19" t="n">
-        <v>0.523</v>
+        <v>0.537</v>
       </c>
       <c r="F79" s="16" t="inlineStr">
         <is>
@@ -3143,10 +3242,10 @@
         </is>
       </c>
       <c r="D80" s="15" t="n">
-        <v>0.976</v>
+        <v>0.97</v>
       </c>
       <c r="E80" s="15" t="n">
-        <v>0.886</v>
+        <v>0.845</v>
       </c>
       <c r="F80" s="20" t="inlineStr">
         <is>
@@ -3165,14 +3264,14 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>ABCDEEGHIJKLMNOPQRST</t>
+          <t>ABCDEFGHIJKLMNOPQRST</t>
         </is>
       </c>
       <c r="D81" s="19" t="n">
-        <v>0.948</v>
+        <v>0.95</v>
       </c>
       <c r="E81" s="19" t="n">
-        <v>0.548</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="F81" s="16" t="inlineStr">
         <is>
@@ -3195,10 +3294,10 @@
         </is>
       </c>
       <c r="D82" s="15" t="n">
-        <v>0.962</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E82" s="15" t="n">
-        <v>0.736</v>
+        <v>0.527</v>
       </c>
       <c r="F82" s="16" t="inlineStr">
         <is>
@@ -3217,18 +3316,18 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>JUMPS-OVER-LAZY-DOG-</t>
+          <t>JUMPS-OVFR-LAZY-DOG-</t>
         </is>
       </c>
       <c r="D83" s="19" t="n">
-        <v>0.974</v>
+        <v>0.966</v>
       </c>
       <c r="E83" s="19" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F83" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.617</v>
+      </c>
+      <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -3243,14 +3342,14 @@
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>PACK-MYIBOX-WITH-TEA</t>
+          <t>PACK-MY-BOX-WITH-TEA</t>
         </is>
       </c>
       <c r="D84" s="15" t="n">
-        <v>0.91</v>
+        <v>0.949</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.081</v>
+        <v>0.695</v>
       </c>
       <c r="F84" s="16" t="inlineStr">
         <is>
@@ -3273,10 +3372,10 @@
         </is>
       </c>
       <c r="D85" s="19" t="n">
-        <v>0.965</v>
+        <v>0.957</v>
       </c>
       <c r="E85" s="19" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.678</v>
       </c>
       <c r="F85" s="16" t="inlineStr">
         <is>
@@ -3299,10 +3398,10 @@
         </is>
       </c>
       <c r="D86" s="15" t="n">
-        <v>0.961</v>
+        <v>0.947</v>
       </c>
       <c r="E86" s="15" t="n">
-        <v>0.574</v>
+        <v>0.608</v>
       </c>
       <c r="F86" s="16" t="inlineStr">
         <is>
@@ -3325,10 +3424,10 @@
         </is>
       </c>
       <c r="D87" s="19" t="n">
-        <v>0.972</v>
+        <v>0.969</v>
       </c>
       <c r="E87" s="19" t="n">
-        <v>0.853</v>
+        <v>0.838</v>
       </c>
       <c r="F87" s="20" t="inlineStr">
         <is>
@@ -3347,14 +3446,14 @@
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>BRIGHT-ZEPHYRS-BLOW-</t>
+          <t>BRIGHT-ZFPHYRS-BLOW-</t>
         </is>
       </c>
       <c r="D88" s="15" t="n">
-        <v>0.957</v>
+        <v>0.949</v>
       </c>
       <c r="E88" s="15" t="n">
-        <v>0.605</v>
+        <v>0.617</v>
       </c>
       <c r="F88" s="16" t="inlineStr">
         <is>
@@ -3373,14 +3472,14 @@
       </c>
       <c r="C89" s="18" t="inlineStr">
         <is>
-          <t>COMPUTIR-VIJTON-TEST</t>
+          <t>COMPUTIR-VISTON-TEST</t>
         </is>
       </c>
       <c r="D89" s="19" t="n">
-        <v>0.897</v>
+        <v>0.883</v>
       </c>
       <c r="E89" s="19" t="n">
-        <v>0.301</v>
+        <v>0.449</v>
       </c>
       <c r="F89" s="16" t="inlineStr">
         <is>
@@ -3399,14 +3498,14 @@
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>MACHTNE-LFARNJNG-AI-</t>
+          <t>MACHTNE-LFARNJNW-AI-</t>
         </is>
       </c>
       <c r="D90" s="15" t="n">
-        <v>0.907</v>
+        <v>0.891</v>
       </c>
       <c r="E90" s="15" t="n">
-        <v>0.359</v>
+        <v>0.366</v>
       </c>
       <c r="F90" s="16" t="inlineStr">
         <is>
@@ -3425,14 +3524,14 @@
       </c>
       <c r="C91" s="18" t="inlineStr">
         <is>
-          <t>DEEP-NEURAL-NETWORKS</t>
+          <t>DEED-NEURAL-NETWORKS</t>
         </is>
       </c>
       <c r="D91" s="19" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="E91" s="19" t="n">
-        <v>0.554</v>
+        <v>0.48</v>
       </c>
       <c r="F91" s="16" t="inlineStr">
         <is>
@@ -3455,10 +3554,10 @@
         </is>
       </c>
       <c r="D92" s="15" t="n">
-        <v>0.954</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E92" s="15" t="n">
-        <v>0.728</v>
+        <v>0.697</v>
       </c>
       <c r="F92" s="16" t="inlineStr">
         <is>
@@ -3481,10 +3580,10 @@
         </is>
       </c>
       <c r="D93" s="19" t="n">
-        <v>0.95</v>
+        <v>0.956</v>
       </c>
       <c r="E93" s="19" t="n">
-        <v>0.554</v>
+        <v>0.67</v>
       </c>
       <c r="F93" s="16" t="inlineStr">
         <is>
@@ -3503,14 +3602,14 @@
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>SMAR--OCR-RECOGNIZF-</t>
+          <t>SMART-OCR-RECOGNIZF-</t>
         </is>
       </c>
       <c r="D94" s="15" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.918</v>
       </c>
       <c r="E94" s="15" t="n">
-        <v>0.59</v>
+        <v>0.662</v>
       </c>
       <c r="F94" s="16" t="inlineStr">
         <is>
@@ -3533,10 +3632,10 @@
         </is>
       </c>
       <c r="D95" s="19" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.923</v>
       </c>
       <c r="E95" s="19" t="n">
-        <v>0.641</v>
+        <v>0.481</v>
       </c>
       <c r="F95" s="16" t="inlineStr">
         <is>
@@ -3559,10 +3658,10 @@
         </is>
       </c>
       <c r="D96" s="15" t="n">
-        <v>0.905</v>
+        <v>0.895</v>
       </c>
       <c r="E96" s="15" t="n">
-        <v>0.527</v>
+        <v>0.624</v>
       </c>
       <c r="F96" s="16" t="inlineStr">
         <is>
@@ -3581,14 +3680,14 @@
       </c>
       <c r="C97" s="18" t="inlineStr">
         <is>
-          <t>HELIO-WORLO-WELCOME-</t>
+          <t>HELLO-KORLO-WELCOMF-</t>
         </is>
       </c>
       <c r="D97" s="19" t="n">
-        <v>0.913</v>
+        <v>0.917</v>
       </c>
       <c r="E97" s="19" t="n">
-        <v>0.413</v>
+        <v>0.586</v>
       </c>
       <c r="F97" s="16" t="inlineStr">
         <is>
@@ -3607,14 +3706,14 @@
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>KNOWLEOGE-IS-PONEE--</t>
+          <t>KNOWLEOGE-IS-POWEF--</t>
         </is>
       </c>
       <c r="D98" s="15" t="n">
-        <v>0.956</v>
+        <v>0.917</v>
       </c>
       <c r="E98" s="15" t="n">
-        <v>0.589</v>
+        <v>0.544</v>
       </c>
       <c r="F98" s="16" t="inlineStr">
         <is>
@@ -3633,14 +3732,14 @@
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>F-ND-EXTRA-FIND-GOLD</t>
+          <t>F-ND-EXTRA-FIND-QOLD</t>
         </is>
       </c>
       <c r="D99" s="19" t="n">
-        <v>0.891</v>
+        <v>0.876</v>
       </c>
       <c r="E99" s="19" t="n">
-        <v>0.47</v>
+        <v>0.513</v>
       </c>
       <c r="F99" s="16" t="inlineStr">
         <is>
@@ -3659,18 +3758,18 @@
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>ZERO-ONE-TWO-SIX-TEN</t>
+          <t>ZERO-ONE-TWO-SIX-TRN</t>
         </is>
       </c>
       <c r="D100" s="15" t="n">
-        <v>0.961</v>
+        <v>0.91</v>
       </c>
       <c r="E100" s="15" t="n">
-        <v>0.834</v>
-      </c>
-      <c r="F100" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.264</v>
+      </c>
+      <c r="F100" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -3689,10 +3788,10 @@
         </is>
       </c>
       <c r="D101" s="19" t="n">
-        <v>0.929</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="E101" s="19" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.712</v>
       </c>
       <c r="F101" s="16" t="inlineStr">
         <is>
@@ -3711,14 +3810,14 @@
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>THE-QUTCK-BROWN-EOX-</t>
+          <t>THE-QUTCK-BROWN-FOX-</t>
         </is>
       </c>
       <c r="D102" s="15" t="n">
-        <v>0.931</v>
+        <v>0.927</v>
       </c>
       <c r="E102" s="15" t="n">
-        <v>0.632</v>
+        <v>0.507</v>
       </c>
       <c r="F102" s="16" t="inlineStr">
         <is>
@@ -3741,10 +3840,10 @@
         </is>
       </c>
       <c r="D103" s="19" t="n">
-        <v>0.952</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="E103" s="19" t="n">
-        <v>0.645</v>
+        <v>0.501</v>
       </c>
       <c r="F103" s="16" t="inlineStr">
         <is>
@@ -3767,10 +3866,10 @@
         </is>
       </c>
       <c r="D104" s="15" t="n">
-        <v>0.955</v>
+        <v>0.953</v>
       </c>
       <c r="E104" s="15" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="F104" s="16" t="inlineStr">
         <is>
@@ -3793,10 +3892,10 @@
         </is>
       </c>
       <c r="D105" s="19" t="n">
-        <v>0.955</v>
+        <v>0.951</v>
       </c>
       <c r="E105" s="19" t="n">
-        <v>0.765</v>
+        <v>0.723</v>
       </c>
       <c r="F105" s="16" t="inlineStr">
         <is>
@@ -3815,14 +3914,14 @@
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>SPHINX-OF-BUACK-GEM-</t>
+          <t>SPHINX-OF-BIACK-GEM-</t>
         </is>
       </c>
       <c r="D106" s="15" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.944</v>
       </c>
       <c r="E106" s="15" t="n">
-        <v>0.445</v>
+        <v>0.593</v>
       </c>
       <c r="F106" s="16" t="inlineStr">
         <is>
@@ -3845,10 +3944,10 @@
         </is>
       </c>
       <c r="D107" s="19" t="n">
-        <v>0.976</v>
+        <v>0.977</v>
       </c>
       <c r="E107" s="19" t="n">
-        <v>0.902</v>
+        <v>0.912</v>
       </c>
       <c r="F107" s="20" t="inlineStr">
         <is>
@@ -3867,14 +3966,14 @@
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>BRIGHT-ZEPHVRS-BLOW-</t>
+          <t>BRIGHT-ZEPHYRS-BLOW-</t>
         </is>
       </c>
       <c r="D108" s="15" t="n">
         <v>0.966</v>
       </c>
       <c r="E108" s="15" t="n">
-        <v>0.665</v>
+        <v>0.778</v>
       </c>
       <c r="F108" s="16" t="inlineStr">
         <is>
@@ -3897,10 +3996,10 @@
         </is>
       </c>
       <c r="D109" s="19" t="n">
-        <v>0.972</v>
+        <v>0.968</v>
       </c>
       <c r="E109" s="19" t="n">
-        <v>0.856</v>
+        <v>0.887</v>
       </c>
       <c r="F109" s="20" t="inlineStr">
         <is>
@@ -3926,7 +4025,7 @@
         <v>0.983</v>
       </c>
       <c r="E110" s="15" t="n">
-        <v>0.906</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F110" s="20" t="inlineStr">
         <is>
@@ -3949,10 +4048,10 @@
         </is>
       </c>
       <c r="D111" s="19" t="n">
-        <v>0.982</v>
+        <v>0.984</v>
       </c>
       <c r="E111" s="19" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.953</v>
       </c>
       <c r="F111" s="20" t="inlineStr">
         <is>
@@ -3971,14 +4070,14 @@
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>TMAG--DATA-DETECT-OK</t>
+          <t>TMAGE-DATA-DETECT-OK</t>
         </is>
       </c>
       <c r="D112" s="15" t="n">
-        <v>0.983</v>
+        <v>0.974</v>
       </c>
       <c r="E112" s="15" t="n">
-        <v>0.893</v>
+        <v>0.852</v>
       </c>
       <c r="F112" s="20" t="inlineStr">
         <is>
@@ -3997,18 +4096,18 @@
       </c>
       <c r="C113" s="18" t="inlineStr">
         <is>
-          <t>P-THON-OPENCV-ROBOT-</t>
+          <t>PYTHON-OPENCV-ROBOT-</t>
         </is>
       </c>
       <c r="D113" s="19" t="n">
-        <v>0.972</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="E113" s="19" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="F113" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.327</v>
+      </c>
+      <c r="F113" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -4027,10 +4126,10 @@
         </is>
       </c>
       <c r="D114" s="15" t="n">
-        <v>0.974</v>
+        <v>0.975</v>
       </c>
       <c r="E114" s="15" t="n">
-        <v>0.872</v>
+        <v>0.902</v>
       </c>
       <c r="F114" s="20" t="inlineStr">
         <is>
@@ -4053,10 +4152,10 @@
         </is>
       </c>
       <c r="D115" s="19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.948</v>
       </c>
       <c r="E115" s="19" t="n">
-        <v>0.583</v>
+        <v>0.702</v>
       </c>
       <c r="F115" s="16" t="inlineStr">
         <is>
@@ -4079,10 +4178,10 @@
         </is>
       </c>
       <c r="D116" s="15" t="n">
-        <v>0.912</v>
+        <v>0.896</v>
       </c>
       <c r="E116" s="15" t="n">
-        <v>0.432</v>
+        <v>0.505</v>
       </c>
       <c r="F116" s="16" t="inlineStr">
         <is>
@@ -4105,10 +4204,10 @@
         </is>
       </c>
       <c r="D117" s="19" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="E117" s="19" t="n">
-        <v>0.345</v>
+        <v>0.745</v>
       </c>
       <c r="F117" s="16" t="inlineStr">
         <is>
@@ -4131,10 +4230,10 @@
         </is>
       </c>
       <c r="D118" s="15" t="n">
-        <v>0.98</v>
+        <v>0.983</v>
       </c>
       <c r="E118" s="15" t="n">
-        <v>0.921</v>
+        <v>0.923</v>
       </c>
       <c r="F118" s="20" t="inlineStr">
         <is>
@@ -4153,18 +4252,18 @@
       </c>
       <c r="C119" s="18" t="inlineStr">
         <is>
-          <t>EIND-EXTRA-EIND-GOLD</t>
+          <t>FIND-EXTRA-FIND-GOLD</t>
         </is>
       </c>
       <c r="D119" s="19" t="n">
-        <v>0.954</v>
+        <v>0.952</v>
       </c>
       <c r="E119" s="19" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F119" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.698</v>
+      </c>
+      <c r="F119" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -4183,10 +4282,10 @@
         </is>
       </c>
       <c r="D120" s="15" t="n">
-        <v>0.977</v>
+        <v>0.972</v>
       </c>
       <c r="E120" s="15" t="n">
-        <v>0.873</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="F120" s="20" t="inlineStr">
         <is>
@@ -4205,14 +4304,14 @@
       </c>
       <c r="C121" s="18" t="inlineStr">
         <is>
-          <t>ABCDEEGHIJKIMNOPORST</t>
+          <t>ABCDEFGHIJKIMNOPORST</t>
         </is>
       </c>
       <c r="D121" s="19" t="n">
-        <v>0.906</v>
+        <v>0.917</v>
       </c>
       <c r="E121" s="19" t="n">
-        <v>0.467</v>
+        <v>0.454</v>
       </c>
       <c r="F121" s="16" t="inlineStr">
         <is>
@@ -4231,14 +4330,14 @@
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>THE-QUICK-BROWN-EOX-</t>
+          <t>THE-QUICK-BROWN-FOX-</t>
         </is>
       </c>
       <c r="D122" s="15" t="n">
-        <v>0.971</v>
+        <v>0.964</v>
       </c>
       <c r="E122" s="15" t="n">
-        <v>0.777</v>
+        <v>0.774</v>
       </c>
       <c r="F122" s="16" t="inlineStr">
         <is>
@@ -4261,14 +4360,14 @@
         </is>
       </c>
       <c r="D123" s="19" t="n">
-        <v>0.977</v>
+        <v>0.971</v>
       </c>
       <c r="E123" s="19" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="F123" s="16" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0.841</v>
+      </c>
+      <c r="F123" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -4283,18 +4382,18 @@
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>PACK-MY-BOXDWITH-TEA</t>
+          <t>PACK-MY-BOXCWITH-TEA</t>
         </is>
       </c>
       <c r="D124" s="15" t="n">
-        <v>0.984</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="E124" s="15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F124" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.215</v>
+      </c>
+      <c r="F124" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -4309,14 +4408,14 @@
       </c>
       <c r="C125" s="18" t="inlineStr">
         <is>
-          <t>EIVE-DOZEN-LIQUOR-JU</t>
+          <t>FIVE-DOZEN-LIQUOR-JU</t>
         </is>
       </c>
       <c r="D125" s="19" t="n">
-        <v>0.969</v>
+        <v>0.959</v>
       </c>
       <c r="E125" s="19" t="n">
-        <v>0.774</v>
+        <v>0.756</v>
       </c>
       <c r="F125" s="16" t="inlineStr">
         <is>
@@ -4335,18 +4434,18 @@
       </c>
       <c r="C126" s="14" t="inlineStr">
         <is>
-          <t>SPHINX-OE-BLACK-CEM-</t>
+          <t>SPHINX-OF-BLACK-CEM-</t>
         </is>
       </c>
       <c r="D126" s="15" t="n">
-        <v>0.963</v>
+        <v>0.96</v>
       </c>
       <c r="E126" s="15" t="n">
-        <v>0.8090000000000001</v>
-      </c>
-      <c r="F126" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.54</v>
+      </c>
+      <c r="F126" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -4365,10 +4464,10 @@
         </is>
       </c>
       <c r="D127" s="19" t="n">
-        <v>0.966</v>
+        <v>0.957</v>
       </c>
       <c r="E127" s="19" t="n">
-        <v>0.725</v>
+        <v>0.787</v>
       </c>
       <c r="F127" s="16" t="inlineStr">
         <is>
@@ -4391,14 +4490,14 @@
         </is>
       </c>
       <c r="D128" s="15" t="n">
-        <v>0.991</v>
+        <v>0.979</v>
       </c>
       <c r="E128" s="15" t="n">
-        <v>0.9419999999999999</v>
-      </c>
-      <c r="F128" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.79</v>
+      </c>
+      <c r="F128" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -4417,10 +4516,10 @@
         </is>
       </c>
       <c r="D129" s="19" t="n">
-        <v>0.956</v>
+        <v>0.963</v>
       </c>
       <c r="E129" s="19" t="n">
-        <v>0.519</v>
+        <v>0.794</v>
       </c>
       <c r="F129" s="16" t="inlineStr">
         <is>
@@ -4439,14 +4538,14 @@
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>MACHINE-CEARNING-AI-</t>
+          <t>MACHINE-LEARNING-AI-</t>
         </is>
       </c>
       <c r="D130" s="15" t="n">
-        <v>0.948</v>
+        <v>0.954</v>
       </c>
       <c r="E130" s="15" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="F130" s="16" t="inlineStr">
         <is>
@@ -4465,14 +4564,14 @@
       </c>
       <c r="C131" s="18" t="inlineStr">
         <is>
-          <t>DEEP-NEURAC-NETWORKV</t>
+          <t>OEEP-NEURAC-NETWORKU</t>
         </is>
       </c>
       <c r="D131" s="19" t="n">
-        <v>0.9</v>
+        <v>0.903</v>
       </c>
       <c r="E131" s="19" t="n">
-        <v>0.258</v>
+        <v>0.197</v>
       </c>
       <c r="F131" s="16" t="inlineStr">
         <is>
@@ -4491,14 +4590,14 @@
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>IMAGE-OATA-DETECT-OK</t>
+          <t>IMAGE-DATA-DETECT-OK</t>
         </is>
       </c>
       <c r="D132" s="15" t="n">
-        <v>0.955</v>
+        <v>0.93</v>
       </c>
       <c r="E132" s="15" t="n">
-        <v>0.597</v>
+        <v>0.551</v>
       </c>
       <c r="F132" s="16" t="inlineStr">
         <is>
@@ -4521,10 +4620,10 @@
         </is>
       </c>
       <c r="D133" s="19" t="n">
-        <v>0.97</v>
+        <v>0.972</v>
       </c>
       <c r="E133" s="19" t="n">
-        <v>0.862</v>
+        <v>0.88</v>
       </c>
       <c r="F133" s="20" t="inlineStr">
         <is>
@@ -4547,10 +4646,10 @@
         </is>
       </c>
       <c r="D134" s="15" t="n">
-        <v>0.982</v>
+        <v>0.971</v>
       </c>
       <c r="E134" s="15" t="n">
-        <v>0.876</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="F134" s="20" t="inlineStr">
         <is>
@@ -4573,10 +4672,10 @@
         </is>
       </c>
       <c r="D135" s="19" t="n">
-        <v>0.977</v>
+        <v>0.981</v>
       </c>
       <c r="E135" s="19" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.888</v>
       </c>
       <c r="F135" s="20" t="inlineStr">
         <is>
@@ -4595,14 +4694,14 @@
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>ARTIEICIAL-SYSTEM-OK</t>
+          <t>ARTIFICIAL-SYSTEM-OK</t>
         </is>
       </c>
       <c r="D136" s="15" t="n">
-        <v>0.957</v>
+        <v>0.952</v>
       </c>
       <c r="E136" s="15" t="n">
-        <v>0.648</v>
+        <v>0.749</v>
       </c>
       <c r="F136" s="16" t="inlineStr">
         <is>
@@ -4621,14 +4720,14 @@
       </c>
       <c r="C137" s="18" t="inlineStr">
         <is>
-          <t>HELLO-WORCD-WELCOME-</t>
+          <t>HELLO-WORLD-WELCOME-</t>
         </is>
       </c>
       <c r="D137" s="19" t="n">
-        <v>0.927</v>
+        <v>0.947</v>
       </c>
       <c r="E137" s="19" t="n">
-        <v>0.496</v>
+        <v>0.667</v>
       </c>
       <c r="F137" s="16" t="inlineStr">
         <is>
@@ -4647,14 +4746,14 @@
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>KNOWLEPGE-IS-POWER--</t>
+          <t>KNOWLEDGE-IS-POWER--</t>
         </is>
       </c>
       <c r="D138" s="15" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="E138" s="15" t="n">
-        <v>0.486</v>
+        <v>0.571</v>
       </c>
       <c r="F138" s="16" t="inlineStr">
         <is>
@@ -4673,14 +4772,14 @@
       </c>
       <c r="C139" s="18" t="inlineStr">
         <is>
-          <t>EIND-EXTRA-EIND-GOLD</t>
+          <t>FIND-EXTRA-FIND-GOLD</t>
         </is>
       </c>
       <c r="D139" s="19" t="n">
         <v>0.944</v>
       </c>
       <c r="E139" s="19" t="n">
-        <v>0.523</v>
+        <v>0.623</v>
       </c>
       <c r="F139" s="16" t="inlineStr">
         <is>
@@ -4703,10 +4802,10 @@
         </is>
       </c>
       <c r="D140" s="15" t="n">
-        <v>0.983</v>
+        <v>0.982</v>
       </c>
       <c r="E140" s="15" t="n">
-        <v>0.946</v>
+        <v>0.91</v>
       </c>
       <c r="F140" s="20" t="inlineStr">
         <is>
@@ -4729,10 +4828,10 @@
         </is>
       </c>
       <c r="D141" s="19" t="n">
-        <v>0.955</v>
+        <v>0.944</v>
       </c>
       <c r="E141" s="19" t="n">
-        <v>0.524</v>
+        <v>0.627</v>
       </c>
       <c r="F141" s="16" t="inlineStr">
         <is>
@@ -4751,14 +4850,14 @@
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>THE-QUICK-BRAWN-EOX-</t>
+          <t>TTE-QUICK-BRAWM-FOX-</t>
         </is>
       </c>
       <c r="D142" s="15" t="n">
-        <v>0.892</v>
+        <v>0.871</v>
       </c>
       <c r="E142" s="15" t="n">
-        <v>0.339</v>
+        <v>0.398</v>
       </c>
       <c r="F142" s="16" t="inlineStr">
         <is>
@@ -4781,10 +4880,10 @@
         </is>
       </c>
       <c r="D143" s="19" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.921</v>
       </c>
       <c r="E143" s="19" t="n">
-        <v>0.618</v>
+        <v>0.426</v>
       </c>
       <c r="F143" s="16" t="inlineStr">
         <is>
@@ -4803,14 +4902,14 @@
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>YACK-MY-BCXIWITH-TEA</t>
+          <t>PACK-MY-BCX-WITH-TEA</t>
         </is>
       </c>
       <c r="D144" s="15" t="n">
-        <v>0.86</v>
+        <v>0.869</v>
       </c>
       <c r="E144" s="15" t="n">
-        <v>0.09</v>
+        <v>0.203</v>
       </c>
       <c r="F144" s="16" t="inlineStr">
         <is>
@@ -4829,14 +4928,14 @@
       </c>
       <c r="C145" s="18" t="inlineStr">
         <is>
-          <t>EIVE-DOZEN-LIQUOR-IU</t>
+          <t>FIVB-DOZEN-LIQUOR-IU</t>
         </is>
       </c>
       <c r="D145" s="19" t="n">
-        <v>0.947</v>
+        <v>0.902</v>
       </c>
       <c r="E145" s="19" t="n">
-        <v>0.695</v>
+        <v>0.373</v>
       </c>
       <c r="F145" s="16" t="inlineStr">
         <is>
@@ -4855,14 +4954,14 @@
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>SPHINX-OR-BLACK-GEY-</t>
+          <t>SPHINX-OR-BLACK-QEY-</t>
         </is>
       </c>
       <c r="D146" s="15" t="n">
-        <v>0.916</v>
+        <v>0.905</v>
       </c>
       <c r="E146" s="15" t="n">
-        <v>0.244</v>
+        <v>0.165</v>
       </c>
       <c r="F146" s="16" t="inlineStr">
         <is>
@@ -4881,18 +4980,18 @@
       </c>
       <c r="C147" s="18" t="inlineStr">
         <is>
-          <t>JUDGE-MY-VOWIQUICKLY</t>
+          <t>JUDGE-MY-VOW-QUICKLY</t>
         </is>
       </c>
       <c r="D147" s="19" t="n">
-        <v>0.93</v>
+        <v>0.962</v>
       </c>
       <c r="E147" s="19" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="F147" s="16" t="inlineStr">
-        <is>
-          <t>YES</t>
+        <v>0.854</v>
+      </c>
+      <c r="F147" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -4911,10 +5010,10 @@
         </is>
       </c>
       <c r="D148" s="15" t="n">
-        <v>0.928</v>
+        <v>0.931</v>
       </c>
       <c r="E148" s="15" t="n">
-        <v>0.217</v>
+        <v>0.351</v>
       </c>
       <c r="F148" s="16" t="inlineStr">
         <is>
@@ -4937,10 +5036,10 @@
         </is>
       </c>
       <c r="D149" s="19" t="n">
-        <v>0.952</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="E149" s="19" t="n">
-        <v>0.62</v>
+        <v>0.398</v>
       </c>
       <c r="F149" s="16" t="inlineStr">
         <is>
@@ -4959,14 +5058,14 @@
       </c>
       <c r="C150" s="14" t="inlineStr">
         <is>
-          <t>MACHINI-LEARNING-AI-</t>
+          <t>MACHINE-LEARNING-AI-</t>
         </is>
       </c>
       <c r="D150" s="15" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="E150" s="15" t="n">
-        <v>0.466</v>
+        <v>0.445</v>
       </c>
       <c r="F150" s="16" t="inlineStr">
         <is>
@@ -4989,10 +5088,10 @@
         </is>
       </c>
       <c r="D151" s="19" t="n">
-        <v>0.88</v>
+        <v>0.913</v>
       </c>
       <c r="E151" s="19" t="n">
-        <v>0.415</v>
+        <v>0.627</v>
       </c>
       <c r="F151" s="16" t="inlineStr">
         <is>
@@ -5011,14 +5110,14 @@
       </c>
       <c r="C152" s="14" t="inlineStr">
         <is>
-          <t>IMAGE-DATA-DETECT-OK</t>
+          <t>IMAGF-DATA-DETECT-OK</t>
         </is>
       </c>
       <c r="D152" s="15" t="n">
-        <v>0.948</v>
+        <v>0.912</v>
       </c>
       <c r="E152" s="15" t="n">
-        <v>0.787</v>
+        <v>0.434</v>
       </c>
       <c r="F152" s="16" t="inlineStr">
         <is>
@@ -5037,14 +5136,14 @@
       </c>
       <c r="C153" s="18" t="inlineStr">
         <is>
-          <t>PYTHON-OPENOV-ROBOT-</t>
+          <t>PYTHON-OPENCV-ROBOT-</t>
         </is>
       </c>
       <c r="D153" s="19" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.948</v>
       </c>
       <c r="E153" s="19" t="n">
-        <v>0.575</v>
+        <v>0.775</v>
       </c>
       <c r="F153" s="16" t="inlineStr">
         <is>
@@ -5067,10 +5166,10 @@
         </is>
       </c>
       <c r="D154" s="15" t="n">
-        <v>0.982</v>
+        <v>0.965</v>
       </c>
       <c r="E154" s="15" t="n">
-        <v>0.885</v>
+        <v>0.841</v>
       </c>
       <c r="F154" s="20" t="inlineStr">
         <is>
@@ -5093,10 +5192,10 @@
         </is>
       </c>
       <c r="D155" s="19" t="n">
-        <v>0.927</v>
+        <v>0.906</v>
       </c>
       <c r="E155" s="19" t="n">
-        <v>0.484</v>
+        <v>0.347</v>
       </c>
       <c r="F155" s="16" t="inlineStr">
         <is>
@@ -5115,14 +5214,14 @@
       </c>
       <c r="C156" s="14" t="inlineStr">
         <is>
-          <t>ARTIEICIALESYSTEM-OK</t>
+          <t>ARTIFICIALESYSTEM-OK</t>
         </is>
       </c>
       <c r="D156" s="15" t="n">
-        <v>0.954</v>
+        <v>0.912</v>
       </c>
       <c r="E156" s="15" t="n">
-        <v>0.587</v>
+        <v>0.387</v>
       </c>
       <c r="F156" s="16" t="inlineStr">
         <is>
@@ -5141,14 +5240,14 @@
       </c>
       <c r="C157" s="18" t="inlineStr">
         <is>
-          <t>HELLO-WORID-WELCOME-</t>
+          <t>HELLO-WORID-WELCOMI-</t>
         </is>
       </c>
       <c r="D157" s="19" t="n">
-        <v>0.901</v>
+        <v>0.897</v>
       </c>
       <c r="E157" s="19" t="n">
-        <v>0.479</v>
+        <v>0.394</v>
       </c>
       <c r="F157" s="16" t="inlineStr">
         <is>
@@ -5167,14 +5266,14 @@
       </c>
       <c r="C158" s="14" t="inlineStr">
         <is>
-          <t>KNOWLEDGE-IS-POWER--</t>
+          <t>KNOWLEDGE-IS-POWBR--</t>
         </is>
       </c>
       <c r="D158" s="15" t="n">
         <v>0.923</v>
       </c>
       <c r="E158" s="15" t="n">
-        <v>0.404</v>
+        <v>0.536</v>
       </c>
       <c r="F158" s="16" t="inlineStr">
         <is>
@@ -5193,14 +5292,14 @@
       </c>
       <c r="C159" s="18" t="inlineStr">
         <is>
-          <t>EIND-EXTRA-FIND-QOLD</t>
+          <t>FIND-EXTRA-FIND-QOLD</t>
         </is>
       </c>
       <c r="D159" s="19" t="n">
-        <v>0.926</v>
+        <v>0.892</v>
       </c>
       <c r="E159" s="19" t="n">
-        <v>0.494</v>
+        <v>0.356</v>
       </c>
       <c r="F159" s="16" t="inlineStr">
         <is>
@@ -5223,14 +5322,14 @@
         </is>
       </c>
       <c r="D160" s="15" t="n">
-        <v>0.977</v>
+        <v>0.944</v>
       </c>
       <c r="E160" s="15" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="F160" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.529</v>
+      </c>
+      <c r="F160" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5245,14 +5344,14 @@
       </c>
       <c r="C161" s="18" t="inlineStr">
         <is>
-          <t>ABODIFGHIJXLMNOPQRST</t>
+          <t>ABCDIFGHIJKLMNOPQRST</t>
         </is>
       </c>
       <c r="D161" s="19" t="n">
-        <v>0.916</v>
+        <v>0.891</v>
       </c>
       <c r="E161" s="19" t="n">
-        <v>0.519</v>
+        <v>0.495</v>
       </c>
       <c r="F161" s="16" t="inlineStr">
         <is>
@@ -5271,18 +5370,18 @@
       </c>
       <c r="C162" s="14" t="inlineStr">
         <is>
-          <t>THE-QUIOK-BROWN-FOX-</t>
+          <t>THE-QUICK-BROWN-FOX-</t>
         </is>
       </c>
       <c r="D162" s="15" t="n">
-        <v>0.973</v>
+        <v>0.96</v>
       </c>
       <c r="E162" s="15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F162" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.765</v>
+      </c>
+      <c r="F162" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5297,11 +5396,11 @@
       </c>
       <c r="C163" s="18" t="inlineStr">
         <is>
-          <t>JUMPS-OVER-LAZY-DOG-</t>
+          <t>IUMPS-OVER-LAZY-OOG-</t>
         </is>
       </c>
       <c r="D163" s="19" t="n">
-        <v>0.966</v>
+        <v>0.95</v>
       </c>
       <c r="E163" s="19" t="n">
         <v>0.616</v>
@@ -5327,14 +5426,14 @@
         </is>
       </c>
       <c r="D164" s="15" t="n">
-        <v>0.981</v>
+        <v>0.955</v>
       </c>
       <c r="E164" s="15" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="F164" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.757</v>
+      </c>
+      <c r="F164" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5349,14 +5448,14 @@
       </c>
       <c r="C165" s="18" t="inlineStr">
         <is>
-          <t>EIVE-DOZEN-LIQUOR-JU</t>
+          <t>FJVE-DOZEN-LIQUOR-IU</t>
         </is>
       </c>
       <c r="D165" s="19" t="n">
-        <v>0.95</v>
+        <v>0.948</v>
       </c>
       <c r="E165" s="19" t="n">
-        <v>0.518</v>
+        <v>0.747</v>
       </c>
       <c r="F165" s="16" t="inlineStr">
         <is>
@@ -5375,14 +5474,14 @@
       </c>
       <c r="C166" s="14" t="inlineStr">
         <is>
-          <t>PHINX-OE-BLACK-GEM--</t>
+          <t>SPHINX-OT-BLACK-GEM-</t>
         </is>
       </c>
       <c r="D166" s="15" t="n">
-        <v>0.972</v>
+        <v>0.926</v>
       </c>
       <c r="E166" s="15" t="n">
-        <v>0.794</v>
+        <v>0.324</v>
       </c>
       <c r="F166" s="16" t="inlineStr">
         <is>
@@ -5401,18 +5500,18 @@
       </c>
       <c r="C167" s="18" t="inlineStr">
         <is>
-          <t>JUDGE-MY-VOW-QUICKLY</t>
+          <t>IUDGF-MY-VOW-QUICKLY</t>
         </is>
       </c>
       <c r="D167" s="19" t="n">
-        <v>0.977</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="E167" s="19" t="n">
-        <v>0.877</v>
-      </c>
-      <c r="F167" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.616</v>
+      </c>
+      <c r="F167" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5427,14 +5526,14 @@
       </c>
       <c r="C168" s="14" t="inlineStr">
         <is>
-          <t>BRIGHTIZEPHYRS-BIOW-</t>
+          <t>BRZGUT-ZFPHYRS-MLOW-</t>
         </is>
       </c>
       <c r="D168" s="15" t="n">
-        <v>0.927</v>
+        <v>0.85</v>
       </c>
       <c r="E168" s="15" t="n">
-        <v>0.167</v>
+        <v>0.496</v>
       </c>
       <c r="F168" s="16" t="inlineStr">
         <is>
@@ -5453,14 +5552,14 @@
       </c>
       <c r="C169" s="18" t="inlineStr">
         <is>
-          <t>COMPUTER-VISION-TESI</t>
+          <t>COMPUTER-VISION-TEST</t>
         </is>
       </c>
       <c r="D169" s="19" t="n">
-        <v>0.962</v>
+        <v>0.885</v>
       </c>
       <c r="E169" s="19" t="n">
-        <v>0.711</v>
+        <v>0.532</v>
       </c>
       <c r="F169" s="16" t="inlineStr">
         <is>
@@ -5483,10 +5582,10 @@
         </is>
       </c>
       <c r="D170" s="15" t="n">
-        <v>0.958</v>
+        <v>0.963</v>
       </c>
       <c r="E170" s="15" t="n">
-        <v>0.55</v>
+        <v>0.797</v>
       </c>
       <c r="F170" s="16" t="inlineStr">
         <is>
@@ -5505,14 +5604,14 @@
       </c>
       <c r="C171" s="18" t="inlineStr">
         <is>
-          <t>DEEP-NEURAL-NETKORKS</t>
+          <t>DEER-NFURAL-NETWORKS</t>
         </is>
       </c>
       <c r="D171" s="19" t="n">
-        <v>0.963</v>
+        <v>0.919</v>
       </c>
       <c r="E171" s="19" t="n">
-        <v>0.781</v>
+        <v>0.15</v>
       </c>
       <c r="F171" s="16" t="inlineStr">
         <is>
@@ -5531,14 +5630,14 @@
       </c>
       <c r="C172" s="14" t="inlineStr">
         <is>
-          <t>TMAGE-DATA-DETECT-OK</t>
+          <t>IMAGE-DATA-DETECT-CK</t>
         </is>
       </c>
       <c r="D172" s="15" t="n">
-        <v>0.951</v>
+        <v>0.879</v>
       </c>
       <c r="E172" s="15" t="n">
-        <v>0.702</v>
+        <v>0.424</v>
       </c>
       <c r="F172" s="16" t="inlineStr">
         <is>
@@ -5561,14 +5660,14 @@
         </is>
       </c>
       <c r="D173" s="19" t="n">
-        <v>0.973</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="E173" s="19" t="n">
-        <v>0.837</v>
-      </c>
-      <c r="F173" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.382</v>
+      </c>
+      <c r="F173" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5583,18 +5682,18 @@
       </c>
       <c r="C174" s="14" t="inlineStr">
         <is>
-          <t>SMART-OCR-RECOGNIZE-</t>
+          <t>SMART-OCR-RECOGNISE-</t>
         </is>
       </c>
       <c r="D174" s="15" t="n">
-        <v>0.988</v>
+        <v>0.902</v>
       </c>
       <c r="E174" s="15" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="F174" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.208</v>
+      </c>
+      <c r="F174" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5609,14 +5708,14 @@
       </c>
       <c r="C175" s="18" t="inlineStr">
         <is>
-          <t>ACCURATE-PREDICTION-</t>
+          <t>ACCURATE-PRFDICTION-</t>
         </is>
       </c>
       <c r="D175" s="19" t="n">
-        <v>0.961</v>
+        <v>0.918</v>
       </c>
       <c r="E175" s="19" t="n">
-        <v>0.694</v>
+        <v>0.53</v>
       </c>
       <c r="F175" s="16" t="inlineStr">
         <is>
@@ -5635,14 +5734,14 @@
       </c>
       <c r="C176" s="14" t="inlineStr">
         <is>
-          <t>ARTIEICIAL-SYSTEM-OK</t>
+          <t>ARTIEZCJAL-SYSTEM-OK</t>
         </is>
       </c>
       <c r="D176" s="15" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="E176" s="15" t="n">
-        <v>0.517</v>
+        <v>0.773</v>
       </c>
       <c r="F176" s="16" t="inlineStr">
         <is>
@@ -5665,14 +5764,14 @@
         </is>
       </c>
       <c r="D177" s="19" t="n">
-        <v>0.976</v>
+        <v>0.909</v>
       </c>
       <c r="E177" s="19" t="n">
-        <v>0.908</v>
-      </c>
-      <c r="F177" s="20" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>0.246</v>
+      </c>
+      <c r="F177" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
     </row>
@@ -5687,14 +5786,14 @@
       </c>
       <c r="C178" s="14" t="inlineStr">
         <is>
-          <t>KNOWLEDGE-IS-POKER--</t>
+          <t>KNOWLEDGE-IS-POWER--</t>
         </is>
       </c>
       <c r="D178" s="15" t="n">
-        <v>0.964</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E178" s="15" t="n">
-        <v>0.637</v>
+        <v>0.555</v>
       </c>
       <c r="F178" s="16" t="inlineStr">
         <is>
@@ -5713,14 +5812,14 @@
       </c>
       <c r="C179" s="18" t="inlineStr">
         <is>
-          <t>EIND-EXTRA-FIND-GOLD</t>
+          <t>HINP-EXTRA-FIND-GGLD</t>
         </is>
       </c>
       <c r="D179" s="19" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.889</v>
       </c>
       <c r="E179" s="19" t="n">
-        <v>0.779</v>
+        <v>0.504</v>
       </c>
       <c r="F179" s="16" t="inlineStr">
         <is>
@@ -5739,14 +5838,14 @@
       </c>
       <c r="C180" s="14" t="inlineStr">
         <is>
-          <t>ZERO-ONE-TWO-SIX-TEN</t>
+          <t>ZERGCONE-TWO-SIX-TEN</t>
         </is>
       </c>
       <c r="D180" s="15" t="n">
-        <v>0.976</v>
+        <v>0.887</v>
       </c>
       <c r="E180" s="15" t="n">
-        <v>0.782</v>
+        <v>0.187</v>
       </c>
       <c r="F180" s="16" t="inlineStr">
         <is>
@@ -5765,23 +5864,1583 @@
       </c>
       <c r="C181" s="18" t="inlineStr">
         <is>
+          <t>ABCDEEGHIJKLMNOPQRST</t>
+        </is>
+      </c>
+      <c r="D181" s="19" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="E181" s="19" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="F181" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="20" customHeight="1">
+      <c r="A182" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B182" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" s="14" t="inlineStr">
+        <is>
+          <t>THE-QUICK-BRUWN-FQX-</t>
+        </is>
+      </c>
+      <c r="D182" s="15" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="E182" s="15" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F182" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1">
+      <c r="A183" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B183" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C183" s="18" t="inlineStr">
+        <is>
+          <t>JUMPS-OVER-LAZY-DOG-</t>
+        </is>
+      </c>
+      <c r="D183" s="19" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="E183" s="19" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="F183" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="20" customHeight="1">
+      <c r="A184" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B184" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C184" s="14" t="inlineStr">
+        <is>
+          <t>PACK-MY-BQX-WITF-TEA</t>
+        </is>
+      </c>
+      <c r="D184" s="15" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="E184" s="15" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="F184" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B185" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C185" s="18" t="inlineStr">
+        <is>
+          <t>FIVEADOZEN-IIQUOR-JU</t>
+        </is>
+      </c>
+      <c r="D185" s="19" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="E185" s="19" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="F185" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B186" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C186" s="14" t="inlineStr">
+        <is>
+          <t>SPHINX-OF-RLACK-GFM-</t>
+        </is>
+      </c>
+      <c r="D186" s="15" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="E186" s="15" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="F186" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B187" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C187" s="18" t="inlineStr">
+        <is>
+          <t>JUDGE-MY-VOW-GUICKLY</t>
+        </is>
+      </c>
+      <c r="D187" s="19" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="E187" s="19" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="F187" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="20" customHeight="1">
+      <c r="A188" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B188" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C188" s="14" t="inlineStr">
+        <is>
+          <t>BRIGHT-ZEPHYRS-BLCW-</t>
+        </is>
+      </c>
+      <c r="D188" s="15" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="E188" s="15" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="F188" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="20" customHeight="1">
+      <c r="A189" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B189" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C189" s="18" t="inlineStr">
+        <is>
+          <t>COMPUTER-VISIQN-TEST</t>
+        </is>
+      </c>
+      <c r="D189" s="19" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="E189" s="19" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="F189" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1">
+      <c r="A190" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B190" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C190" s="14" t="inlineStr">
+        <is>
+          <t>OACHINE-LFARNING-AI-</t>
+        </is>
+      </c>
+      <c r="D190" s="15" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="E190" s="15" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="F190" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1">
+      <c r="A191" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B191" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C191" s="18" t="inlineStr">
+        <is>
+          <t>DEEP-NEURAL-NETWQRKS</t>
+        </is>
+      </c>
+      <c r="D191" s="19" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="E191" s="19" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="F191" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1">
+      <c r="A192" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B192" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C192" s="14" t="inlineStr">
+        <is>
+          <t>IMAGE-DATA-DFTECT-OK</t>
+        </is>
+      </c>
+      <c r="D192" s="15" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="E192" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F192" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B193" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C193" s="18" t="inlineStr">
+        <is>
+          <t>PYTHUN-OPENCV-BOBOT-</t>
+        </is>
+      </c>
+      <c r="D193" s="19" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E193" s="19" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="F193" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="20" customHeight="1">
+      <c r="A194" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B194" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C194" s="14" t="inlineStr">
+        <is>
+          <t>SMART-OCR-RECOGNIZF-</t>
+        </is>
+      </c>
+      <c r="D194" s="15" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="E194" s="15" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="F194" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="20" customHeight="1">
+      <c r="A195" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B195" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C195" s="18" t="inlineStr">
+        <is>
+          <t>ACCURATE-PREDICTIDN-</t>
+        </is>
+      </c>
+      <c r="D195" s="19" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="E195" s="19" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="F195" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="20" customHeight="1">
+      <c r="A196" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B196" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C196" s="14" t="inlineStr">
+        <is>
+          <t>ARTIFICIAL-EHEDICTIO</t>
+        </is>
+      </c>
+      <c r="D196" s="15" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="E196" s="15" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="F196" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="20" customHeight="1">
+      <c r="A197" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B197" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C197" s="18" t="inlineStr">
+        <is>
+          <t>HELLO-WORLD-WFLCOME-</t>
+        </is>
+      </c>
+      <c r="D197" s="19" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="E197" s="19" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="F197" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="20" customHeight="1">
+      <c r="A198" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B198" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C198" s="14" t="inlineStr">
+        <is>
+          <t>KNOWLEDGE-LS-POWFR--</t>
+        </is>
+      </c>
+      <c r="D198" s="15" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="E198" s="15" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="F198" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="20" customHeight="1">
+      <c r="A199" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B199" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="C199" s="18" t="inlineStr">
+        <is>
+          <t>FIND-EXTRA-FLNK-GOID</t>
+        </is>
+      </c>
+      <c r="D199" s="19" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="E199" s="19" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="F199" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="20" customHeight="1">
+      <c r="A200" s="13" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B200" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="C200" s="14" t="inlineStr">
+        <is>
+          <t>ZEBO-ONE-TWU-CIX-TEN</t>
+        </is>
+      </c>
+      <c r="D200" s="15" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E200" s="15" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="F200" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="20" customHeight="1">
+      <c r="A201" s="17" t="inlineStr">
+        <is>
+          <t>test10.jpg</t>
+        </is>
+      </c>
+      <c r="B201" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C201" s="18" t="inlineStr">
+        <is>
+          <t>ABCDEFGHIGKLMNCKGPST</t>
+        </is>
+      </c>
+      <c r="D201" s="19" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="E201" s="19" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="F201" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="20" customHeight="1">
+      <c r="A202" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B202" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" s="14" t="inlineStr">
+        <is>
+          <t>IHE-QUICK-BROWN-FOX-</t>
+        </is>
+      </c>
+      <c r="D202" s="15" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="E202" s="15" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="F202" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="20" customHeight="1">
+      <c r="A203" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B203" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C203" s="18" t="inlineStr">
+        <is>
+          <t>JUMPS-OVER-LAZY-DOG-</t>
+        </is>
+      </c>
+      <c r="D203" s="19" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="E203" s="19" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="F203" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="20" customHeight="1">
+      <c r="A204" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B204" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C204" s="14" t="inlineStr">
+        <is>
+          <t>PACK-MY-BOX-WITH-TEA</t>
+        </is>
+      </c>
+      <c r="D204" s="15" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="E204" s="15" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="F204" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="20" customHeight="1">
+      <c r="A205" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B205" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C205" s="18" t="inlineStr">
+        <is>
+          <t>FIVE-DOZEN-LIQUOR-JU</t>
+        </is>
+      </c>
+      <c r="D205" s="19" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="E205" s="19" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="F205" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="20" customHeight="1">
+      <c r="A206" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B206" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C206" s="14" t="inlineStr">
+        <is>
+          <t>SPHINX-OF-BLACK-GEM-</t>
+        </is>
+      </c>
+      <c r="D206" s="15" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="E206" s="15" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F206" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="20" customHeight="1">
+      <c r="A207" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B207" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C207" s="18" t="inlineStr">
+        <is>
+          <t>JUDGE-MY-VOW-QUICKLY</t>
+        </is>
+      </c>
+      <c r="D207" s="19" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E207" s="19" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="F207" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="20" customHeight="1">
+      <c r="A208" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B208" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C208" s="14" t="inlineStr">
+        <is>
+          <t>BRIGHT-ZEPHYRS-BIOW-</t>
+        </is>
+      </c>
+      <c r="D208" s="15" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="E208" s="15" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="F208" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="20" customHeight="1">
+      <c r="A209" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B209" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C209" s="18" t="inlineStr">
+        <is>
+          <t>COMPUTER-VISION-TEST</t>
+        </is>
+      </c>
+      <c r="D209" s="19" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="E209" s="19" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="F209" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="20" customHeight="1">
+      <c r="A210" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B210" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C210" s="14" t="inlineStr">
+        <is>
+          <t>MACHINE-LEARNING-AI-</t>
+        </is>
+      </c>
+      <c r="D210" s="15" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="E210" s="15" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="F210" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="20" customHeight="1">
+      <c r="A211" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B211" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C211" s="18" t="inlineStr">
+        <is>
+          <t>DEEP-NEURAL-NFTKORKS</t>
+        </is>
+      </c>
+      <c r="D211" s="19" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="E211" s="19" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="F211" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="20" customHeight="1">
+      <c r="A212" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B212" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C212" s="14" t="inlineStr">
+        <is>
+          <t>IMAGE-DATA-DETECT-OK</t>
+        </is>
+      </c>
+      <c r="D212" s="15" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="E212" s="15" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="F212" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="20" customHeight="1">
+      <c r="A213" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B213" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C213" s="18" t="inlineStr">
+        <is>
+          <t>PYTHON-OPENCV-ROBOT-</t>
+        </is>
+      </c>
+      <c r="D213" s="19" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="E213" s="19" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="F213" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="20" customHeight="1">
+      <c r="A214" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B214" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C214" s="14" t="inlineStr">
+        <is>
+          <t>SMART-OCR-RECOGNIZE-</t>
+        </is>
+      </c>
+      <c r="D214" s="15" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="E214" s="15" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="F214" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="20" customHeight="1">
+      <c r="A215" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B215" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C215" s="18" t="inlineStr">
+        <is>
+          <t>ACCURATE-PREDICTION-</t>
+        </is>
+      </c>
+      <c r="D215" s="19" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="E215" s="19" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="F215" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="20" customHeight="1">
+      <c r="A216" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B216" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C216" s="14" t="inlineStr">
+        <is>
+          <t>ARTIFICIAL-SYSTEM-OK</t>
+        </is>
+      </c>
+      <c r="D216" s="15" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="E216" s="15" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="F216" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="20" customHeight="1">
+      <c r="A217" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B217" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C217" s="18" t="inlineStr">
+        <is>
+          <t>HELLO-WORLD-WELCOME-</t>
+        </is>
+      </c>
+      <c r="D217" s="19" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="E217" s="19" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="F217" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="20" customHeight="1">
+      <c r="A218" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B218" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C218" s="14" t="inlineStr">
+        <is>
+          <t>KNOWLEDGE-IS-POKER--</t>
+        </is>
+      </c>
+      <c r="D218" s="15" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E218" s="15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F218" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="20" customHeight="1">
+      <c r="A219" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B219" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="C219" s="18" t="inlineStr">
+        <is>
+          <t>FIND-EXTRA-FIND-GOLD</t>
+        </is>
+      </c>
+      <c r="D219" s="19" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="E219" s="19" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="F219" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="20" customHeight="1">
+      <c r="A220" s="13" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B220" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="C220" s="14" t="inlineStr">
+        <is>
+          <t>ZERO-ONE-TWO-SIX-TEN</t>
+        </is>
+      </c>
+      <c r="D220" s="15" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="E220" s="15" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="F220" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="20" customHeight="1">
+      <c r="A221" s="17" t="inlineStr">
+        <is>
+          <t>test11.jpg</t>
+        </is>
+      </c>
+      <c r="B221" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C221" s="18" t="inlineStr">
+        <is>
+          <t>ABCDEFGHIJKLMNQPQRST</t>
+        </is>
+      </c>
+      <c r="D221" s="19" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="E221" s="19" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="F221" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="20" customHeight="1">
+      <c r="A222" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B222" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" s="14" t="inlineStr">
+        <is>
+          <t>THE-QUICK-BROWN-FOX-</t>
+        </is>
+      </c>
+      <c r="D222" s="15" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E222" s="15" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="F222" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="20" customHeight="1">
+      <c r="A223" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B223" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C223" s="18" t="inlineStr">
+        <is>
+          <t>JUMPS-OVER-LAZY-DOG-</t>
+        </is>
+      </c>
+      <c r="D223" s="19" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="E223" s="19" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="F223" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="20" customHeight="1">
+      <c r="A224" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B224" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C224" s="14" t="inlineStr">
+        <is>
+          <t>PACK-MY-BOX-WITH-TEA</t>
+        </is>
+      </c>
+      <c r="D224" s="15" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="E224" s="15" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="F224" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="20" customHeight="1">
+      <c r="A225" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B225" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C225" s="18" t="inlineStr">
+        <is>
+          <t>FIVE-DOZEN-LIQUOR-JU</t>
+        </is>
+      </c>
+      <c r="D225" s="19" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E225" s="19" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="F225" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="20" customHeight="1">
+      <c r="A226" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B226" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C226" s="14" t="inlineStr">
+        <is>
+          <t>SPHINX-OF-BLACK-GEM-</t>
+        </is>
+      </c>
+      <c r="D226" s="15" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E226" s="15" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="F226" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="20" customHeight="1">
+      <c r="A227" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B227" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C227" s="18" t="inlineStr">
+        <is>
+          <t>JUDGE-MY-VOW-QUICKLY</t>
+        </is>
+      </c>
+      <c r="D227" s="19" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="E227" s="19" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="F227" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="20" customHeight="1">
+      <c r="A228" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B228" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C228" s="14" t="inlineStr">
+        <is>
+          <t>BRIGHT-ZEPHYRS-BLOW-</t>
+        </is>
+      </c>
+      <c r="D228" s="15" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E228" s="15" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="F228" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="20" customHeight="1">
+      <c r="A229" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B229" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C229" s="18" t="inlineStr">
+        <is>
+          <t>COMPUTER-VISION-TEST</t>
+        </is>
+      </c>
+      <c r="D229" s="19" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="E229" s="19" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="F229" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="20" customHeight="1">
+      <c r="A230" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B230" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C230" s="14" t="inlineStr">
+        <is>
+          <t>MECHINE-LEARNING-AI-</t>
+        </is>
+      </c>
+      <c r="D230" s="15" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E230" s="15" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="F230" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="20" customHeight="1">
+      <c r="A231" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B231" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C231" s="18" t="inlineStr">
+        <is>
+          <t>DEEP-NEURAL-NETWORKS</t>
+        </is>
+      </c>
+      <c r="D231" s="19" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="E231" s="19" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="F231" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="20" customHeight="1">
+      <c r="A232" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B232" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C232" s="14" t="inlineStr">
+        <is>
+          <t>IMAGE-DATA-OETECT-OK</t>
+        </is>
+      </c>
+      <c r="D232" s="15" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E232" s="15" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="F232" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="20" customHeight="1">
+      <c r="A233" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B233" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C233" s="18" t="inlineStr">
+        <is>
+          <t>PYTHON-OPENCV-ROBOT-</t>
+        </is>
+      </c>
+      <c r="D233" s="19" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="E233" s="19" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="F233" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="20" customHeight="1">
+      <c r="A234" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B234" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C234" s="14" t="inlineStr">
+        <is>
+          <t>SMART-OCR-RECOGNIZE-</t>
+        </is>
+      </c>
+      <c r="D234" s="15" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="E234" s="15" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="F234" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="20" customHeight="1">
+      <c r="A235" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B235" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C235" s="18" t="inlineStr">
+        <is>
+          <t>ACCURATE-PREDICTION-</t>
+        </is>
+      </c>
+      <c r="D235" s="19" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="E235" s="19" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F235" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="20" customHeight="1">
+      <c r="A236" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B236" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C236" s="14" t="inlineStr">
+        <is>
+          <t>ARTIFICIAL-SYSTEM-OK</t>
+        </is>
+      </c>
+      <c r="D236" s="15" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="E236" s="15" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="F236" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="20" customHeight="1">
+      <c r="A237" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B237" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C237" s="18" t="inlineStr">
+        <is>
+          <t>HELLO-WORLD-WELCOME-</t>
+        </is>
+      </c>
+      <c r="D237" s="19" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E237" s="19" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="F237" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="20" customHeight="1">
+      <c r="A238" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B238" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C238" s="14" t="inlineStr">
+        <is>
+          <t>KNOWLEDGE-IS-POWER--</t>
+        </is>
+      </c>
+      <c r="D238" s="15" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="E238" s="15" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="F238" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="20" customHeight="1">
+      <c r="A239" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B239" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="C239" s="18" t="inlineStr">
+        <is>
+          <t>FIND-EXTRA-FINO-GOLD</t>
+        </is>
+      </c>
+      <c r="D239" s="19" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="E239" s="19" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="F239" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="20" customHeight="1">
+      <c r="A240" s="13" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B240" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="C240" s="14" t="inlineStr">
+        <is>
+          <t>ZERO-ONE-TWO-SIX-TEN</t>
+        </is>
+      </c>
+      <c r="D240" s="15" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="E240" s="15" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="F240" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="20" customHeight="1">
+      <c r="A241" s="17" t="inlineStr">
+        <is>
+          <t>test12.jpg</t>
+        </is>
+      </c>
+      <c r="B241" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C241" s="18" t="inlineStr">
+        <is>
           <t>ABCDEFGHIJKLMNOPQRST</t>
         </is>
       </c>
-      <c r="D181" s="19" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="E181" s="19" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="F181" s="16" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="D241" s="19" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="E241" s="19" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="F241" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F181"/>
+  <autoFilter ref="A1:F241"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/results/all_results_cnn.xlsx
+++ b/outputs/results/all_results_cnn.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed_Results" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detailed_Results'!$A$1:$F$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detailed_Results'!$A$1:$F$261</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>สร้างรายงานเมื่อ: 2026-10-26 14:43:36 | โมเดลที่ใช้ตรวจ: Custom 2D CNN | ตรวจทั้งหมด: 12 แผ่น | รวม 240 ข้อ</t>
+          <t>สร้างรายงานเมื่อ: 2026-10-28 16:33:19 | โมเดลที่ใช้ตรวจ: Custom 2D CNN | ตรวจทั้งหมด: 13 แผ่น | รวม 260 ข้อ</t>
         </is>
       </c>
     </row>
@@ -676,27 +676,27 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>12 แผ่น</t>
+          <t>13 แผ่น</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>240 ข้อ</t>
+          <t>260 ข้อ</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>4,800 ตัว</t>
+          <t>5,200 ตัว</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>95.04%</t>
+          <t>95.25%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>185 ข้อ</t>
+          <t>205 ข้อ</t>
         </is>
       </c>
     </row>
@@ -1137,6 +1137,39 @@
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>English &amp; Tech (ชุดที่ 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>97.75%</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>0.926</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>20 ข้อ</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>English &amp; Tech (ชุดที่ 1)</t>
         </is>
@@ -1156,7 +1189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F241"/>
+  <dimension ref="A1:F261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7439,8 +7472,528 @@
         </is>
       </c>
     </row>
+    <row r="242" ht="20" customHeight="1">
+      <c r="A242" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B242" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" s="14" t="inlineStr">
+        <is>
+          <t>THE-QUICK-BROWN-FOX-</t>
+        </is>
+      </c>
+      <c r="D242" s="15" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E242" s="15" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="F242" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="20" customHeight="1">
+      <c r="A243" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B243" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C243" s="18" t="inlineStr">
+        <is>
+          <t>JUMPS-OVER-LAZY-DOG-</t>
+        </is>
+      </c>
+      <c r="D243" s="19" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="E243" s="19" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="F243" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="20" customHeight="1">
+      <c r="A244" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B244" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C244" s="14" t="inlineStr">
+        <is>
+          <t>PACU-MY-BOX-WITH-TEA</t>
+        </is>
+      </c>
+      <c r="D244" s="15" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="E244" s="15" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="F244" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="20" customHeight="1">
+      <c r="A245" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B245" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C245" s="18" t="inlineStr">
+        <is>
+          <t>EIVE-DOZEN-LIQUOR-JU</t>
+        </is>
+      </c>
+      <c r="D245" s="19" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="E245" s="19" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F245" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="20" customHeight="1">
+      <c r="A246" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B246" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C246" s="14" t="inlineStr">
+        <is>
+          <t>SPHINX-OF-BLACK-GEM-</t>
+        </is>
+      </c>
+      <c r="D246" s="15" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="E246" s="15" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="F246" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="20" customHeight="1">
+      <c r="A247" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B247" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C247" s="18" t="inlineStr">
+        <is>
+          <t>JUDGE-MY-VOW-QUICKLY</t>
+        </is>
+      </c>
+      <c r="D247" s="19" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="E247" s="19" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="F247" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="20" customHeight="1">
+      <c r="A248" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B248" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C248" s="14" t="inlineStr">
+        <is>
+          <t>BRIGHT-ZEPHYRS-BLOW-</t>
+        </is>
+      </c>
+      <c r="D248" s="15" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="E248" s="15" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="F248" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="20" customHeight="1">
+      <c r="A249" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B249" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C249" s="18" t="inlineStr">
+        <is>
+          <t>COMPUTER-VISION-TEST</t>
+        </is>
+      </c>
+      <c r="D249" s="19" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="E249" s="19" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="F249" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="20" customHeight="1">
+      <c r="A250" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B250" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C250" s="14" t="inlineStr">
+        <is>
+          <t>MECHINE-LEARNING-AI-</t>
+        </is>
+      </c>
+      <c r="D250" s="15" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="E250" s="15" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="F250" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="20" customHeight="1">
+      <c r="A251" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B251" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C251" s="18" t="inlineStr">
+        <is>
+          <t>DEEP-NEURAL-NETWORKS</t>
+        </is>
+      </c>
+      <c r="D251" s="19" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E251" s="19" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="F251" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="20" customHeight="1">
+      <c r="A252" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B252" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C252" s="14" t="inlineStr">
+        <is>
+          <t>IMAGE-OAIA-OETECT-OK</t>
+        </is>
+      </c>
+      <c r="D252" s="15" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="E252" s="15" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="F252" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="20" customHeight="1">
+      <c r="A253" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B253" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C253" s="18" t="inlineStr">
+        <is>
+          <t>PYTHON-OPENCV-ROBOT-</t>
+        </is>
+      </c>
+      <c r="D253" s="19" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="E253" s="19" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="F253" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="20" customHeight="1">
+      <c r="A254" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B254" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C254" s="14" t="inlineStr">
+        <is>
+          <t>SMART-OCR-RECOGNIZE-</t>
+        </is>
+      </c>
+      <c r="D254" s="15" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="E254" s="15" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="F254" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="20" customHeight="1">
+      <c r="A255" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B255" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C255" s="18" t="inlineStr">
+        <is>
+          <t>ACCURATE-PREDICTION-</t>
+        </is>
+      </c>
+      <c r="D255" s="19" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="E255" s="19" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="F255" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="20" customHeight="1">
+      <c r="A256" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B256" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C256" s="14" t="inlineStr">
+        <is>
+          <t>ARTIFICIAL-SYSTEM-OK</t>
+        </is>
+      </c>
+      <c r="D256" s="15" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E256" s="15" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="F256" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="20" customHeight="1">
+      <c r="A257" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B257" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C257" s="18" t="inlineStr">
+        <is>
+          <t>HELLO-WORLD-WELCOME-</t>
+        </is>
+      </c>
+      <c r="D257" s="19" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="E257" s="19" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="F257" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="20" customHeight="1">
+      <c r="A258" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B258" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="C258" s="14" t="inlineStr">
+        <is>
+          <t>KNOWLEDGE-IS-POWER--</t>
+        </is>
+      </c>
+      <c r="D258" s="15" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="E258" s="15" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="F258" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="20" customHeight="1">
+      <c r="A259" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B259" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="C259" s="18" t="inlineStr">
+        <is>
+          <t>FIND-EXTRA-FIND-GOLO</t>
+        </is>
+      </c>
+      <c r="D259" s="19" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="E259" s="19" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="F259" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="20" customHeight="1">
+      <c r="A260" s="13" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B260" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="C260" s="14" t="inlineStr">
+        <is>
+          <t>ZERO-ONE-TWO-SIX-TEN</t>
+        </is>
+      </c>
+      <c r="D260" s="15" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="E260" s="15" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="F260" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="20" customHeight="1">
+      <c r="A261" s="17" t="inlineStr">
+        <is>
+          <t>test13.jpg</t>
+        </is>
+      </c>
+      <c r="B261" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C261" s="18" t="inlineStr">
+        <is>
+          <t>KBCDEFGHIJKLMNOPQRST</t>
+        </is>
+      </c>
+      <c r="D261" s="19" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="E261" s="19" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="F261" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F241"/>
+  <autoFilter ref="A1:F261"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>